--- a/sheets/대금율보/검수/미운 사랑.xlsx
+++ b/sheets/대금율보/검수/미운 사랑.xlsx
@@ -5274,17 +5274,9 @@
       <c r="E4" s="25"/>
       <c r="F4" s="23"/>
       <c r="G4" s="25"/>
-      <c r="H4" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H4" s="23"/>
       <c r="I4" s="25"/>
-      <c r="J4" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J4" s="23"/>
       <c r="K4" s="25"/>
       <c r="L4" s="23"/>
       <c r="M4" s="25"/>
@@ -5293,7 +5285,7 @@
       <c r="A5" s="0"/>
       <c r="B5" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="C5" s="25"/>
@@ -5914,7 +5906,7 @@
       </c>
       <c r="L17" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="M17" s="25"/>

--- a/sheets/대금율보/검수/미운 사랑.xlsx
+++ b/sheets/대금율보/검수/미운 사랑.xlsx
@@ -5174,24 +5174,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="93.02" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="69.36" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
       <c r="L3" s="23"/>
       <c r="M3" s="24"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="69.36" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="23" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
       <c r="L4" s="23"/>
       <c r="M4" s="25"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="69.36" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="23" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="M5" s="25"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="69.36" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="23" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="M6" s="26"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="69.36" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="23" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
       </c>
       <c r="M7" s="24"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="69.36" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="23" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
       </c>
       <c r="M8" s="25"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="69.36" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="23" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
       </c>
       <c r="M9" s="25"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="69.36" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="23" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="M10" s="27"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="69.36" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="23" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="M11" s="24"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="69.36" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="23"/>
       <c r="C12" s="25"/>
@@ -5676,7 +5676,7 @@
       </c>
       <c r="M12" s="25"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="69.36" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="23"/>
       <c r="C13" s="25"/>
@@ -5708,7 +5708,7 @@
       </c>
       <c r="M13" s="25"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="69.36" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="23" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
       </c>
       <c r="M14" s="26"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="69.36" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="23" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="M15" s="24"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="69.36" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="23" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="M16" s="25"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="69.36" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="23" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
       </c>
       <c r="M17" s="25"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="69.36" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
       </c>
       <c r="M18" s="26"/>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="69.36" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="23" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="M19" s="24"/>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="69.36" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="23" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
       <c r="L20" s="23"/>
       <c r="M20" s="25"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="69.36" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="23" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
       <c r="L21" s="23"/>
       <c r="M21" s="25"/>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="69.36" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="23" t="inlineStr">
         <is>
@@ -6154,7 +6154,7 @@
       <c r="L22" s="23"/>
       <c r="M22" s="26"/>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="69.36" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="23" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="69.36" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="23" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="56" customHeight="1">
+    <row r="25" ht="69.36" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="23" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="69.36" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="23" t="inlineStr">
         <is>
@@ -6389,6 +6389,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="52"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="43"/>
 </worksheet>
 </file>